--- a/results/Int All Data 1.0/Rando_fi_explain.xlsx
+++ b/results/Int All Data 1.0/Rando_fi_explain.xlsx
@@ -1676,466 +1676,466 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0008395265606421388</v>
+        <v>0.0004403219980650409</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.0001378829894027822</v>
+        <v>-0.0005907974444116914</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0004669569909994231</v>
+        <v>-0.0006900552603654841</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005895795776367319</v>
+        <v>0.0001450985980195874</v>
       </c>
       <c r="F3" t="n">
-        <v>-4.292450117876711e-05</v>
+        <v>-0.0001825418820810509</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001298777310432939</v>
+        <v>0.0009189463179627089</v>
       </c>
       <c r="H3" t="n">
-        <v>-5.368082642148276e-05</v>
+        <v>-0.0002100746801973252</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0002693617434951778</v>
+        <v>0.0002171669258945796</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0009831934140267385</v>
+        <v>-0.0001080413315776341</v>
       </c>
       <c r="K3" t="n">
-        <v>6.987090047689271e-05</v>
+        <v>-4.552118085591527e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0001198039108192062</v>
+        <v>-3.376029913373268e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>-4.467852166687435e-05</v>
+        <v>-0.0001098482414718105</v>
       </c>
       <c r="N3" t="n">
-        <v>9.283139493838522e-05</v>
+        <v>0.0002667649286710994</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0003884082225423768</v>
+        <v>-0.000507739609699196</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0004161227014080515</v>
+        <v>0.0004152254098163844</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.001994211683204177</v>
+        <v>0.000998052165509442</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.0002755462140270315</v>
+        <v>-0.0008489849458586662</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0001561552360704166</v>
+        <v>0.000789220242645059</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0001500634169408499</v>
+        <v>6.963304366792728e-06</v>
       </c>
       <c r="U3" t="n">
-        <v>4.537227589242799e-05</v>
+        <v>-0.0001372617397745734</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0002142776057217345</v>
+        <v>0.0005201913515784662</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0001092852209830475</v>
+        <v>-0.0003127810188845915</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0004857054072623901</v>
+        <v>0.00141034015235533</v>
       </c>
       <c r="Y3" t="n">
-        <v>-8.697072355834612e-05</v>
+        <v>-0.0002632368282909225</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0006370875266525411</v>
+        <v>-3.477202308480584e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>9.862063788127706e-05</v>
+        <v>0.000138148654680511</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.180674983846333e-05</v>
+        <v>-4.404869021589984e-05</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.0005526425480825092</v>
+        <v>0.0005219970091693616</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.002119343055448967</v>
+        <v>0.003253527770006743</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.01145889609309715</v>
+        <v>0.01424418825682242</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.0008037632308472521</v>
+        <v>0.0003705565891749639</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.0005151579426257502</v>
+        <v>0.0004254517073304365</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.0006965084732419446</v>
+        <v>0.0002228347933448594</v>
       </c>
       <c r="AI3" t="n">
-        <v>-9.969217546278442e-05</v>
+        <v>-0.000356632480699196</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.003235690670040858</v>
+        <v>0.001972098645770273</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.01810257168529655</v>
+        <v>0.01726227671894073</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.0004869121738160731</v>
+        <v>0.0001348149322260406</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.005603110462790438</v>
+        <v>0.004139187690047651</v>
       </c>
       <c r="AN3" t="n">
-        <v>-0.0001453031445958942</v>
+        <v>0.0008655082594707852</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.001311611125321733</v>
+        <v>0.0002965561078548196</v>
       </c>
       <c r="AP3" t="n">
-        <v>9.681433275497975e-05</v>
+        <v>-0.000261769550588492</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.0001540281452554093</v>
+        <v>0.0004084832246317172</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.01184342948651959</v>
+        <v>0.01063803045717155</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.0001410019229465864</v>
+        <v>2.828747434538982e-05</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.0004095602716875479</v>
+        <v>4.511520272483469e-05</v>
       </c>
       <c r="AU3" t="n">
-        <v>-1.852085681990691e-05</v>
+        <v>-7.689102747261645e-05</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.0009164485775922614</v>
+        <v>0.0004224182158101931</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.001057170720746166</v>
+        <v>0.0005059914914790398</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.517077629408448e-05</v>
+        <v>0.0001581947461799949</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.0003719377522434753</v>
+        <v>-0.0001149136045800425</v>
       </c>
       <c r="AZ3" t="n">
-        <v>3.708537732442729e-05</v>
+        <v>0.0003500797267457012</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.0007816315633443705</v>
+        <v>0.0007053068102383474</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.0003963149312684832</v>
+        <v>0.001391685889124677</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.000107709786340876</v>
+        <v>-0.0001637837343680915</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.0001233409730394563</v>
+        <v>-0.0001299953458384806</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.0004268380613414236</v>
+        <v>-0.000232853761593037</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.001745218870226938</v>
+        <v>0.002463851408408514</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.0001881043195851262</v>
+        <v>6.995248911723764e-05</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.0004254610117091318</v>
+        <v>0.0002168804485523923</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.002845177900575895</v>
+        <v>0.003251745123659131</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.0004939203401415537</v>
+        <v>-0.000855868418724881</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.0004322730450519141</v>
+        <v>0.0002445373129494676</v>
       </c>
       <c r="BL3" t="n">
-        <v>-4.821942658169042e-05</v>
+        <v>-5.504950432506761e-05</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.0005909580964707761</v>
+        <v>0.0003980011151252172</v>
       </c>
       <c r="BN3" t="n">
-        <v>-6.35473173942502e-05</v>
+        <v>5.227411442051514e-05</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.0004729248032802535</v>
+        <v>-0.00168489351492767</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0.002708396339998336</v>
+        <v>-0.002852219879056287</v>
       </c>
       <c r="BQ3" t="n">
         <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>-0.0002672368667014003</v>
+        <v>-0.0006361653044025451</v>
       </c>
       <c r="BS3" t="n">
-        <v>-0.0010146208822408</v>
+        <v>-0.0007266028515998958</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.0001062176224106348</v>
+        <v>1.628931401689515e-05</v>
       </c>
       <c r="BU3" t="n">
-        <v>-0.001183575094834525</v>
+        <v>-0.003551256591711514</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0.0003104028459914354</v>
+        <v>-6.02253439674616e-05</v>
       </c>
       <c r="BW3" t="n">
-        <v>3.690541279389725e-06</v>
+        <v>1.204701830205268e-06</v>
       </c>
       <c r="BX3" t="n">
-        <v>-0.0003817937524583259</v>
+        <v>-0.002911912979236717</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.0002164231574486331</v>
+        <v>0.0007920121049991546</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.001760410901124405</v>
+        <v>0.001263132827775274</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.0005685125542871826</v>
+        <v>-4.457465149562466e-05</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.458813656004202e-05</v>
+        <v>-0.002065914244409248</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.0001592965984557493</v>
+        <v>-0.0001666724399048314</v>
       </c>
       <c r="CD3" t="n">
-        <v>6.831358442997964e-06</v>
+        <v>5.350561198268153e-05</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0.0002354820199452767</v>
+        <v>-0.0004146987180158834</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0.000199684817644108</v>
+        <v>-0.00190963564573789</v>
       </c>
       <c r="CG3" t="n">
-        <v>-0.0007169859645896303</v>
+        <v>-0.003090602424989948</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.0004077601815829379</v>
+        <v>-0.0001680841645234166</v>
       </c>
       <c r="CI3" t="n">
-        <v>-0.0003554495643532552</v>
+        <v>-0.002835505566617849</v>
       </c>
       <c r="CJ3" t="n">
-        <v>-1.075268817204211e-05</v>
+        <v>4.119814830853219e-05</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.0003753015528373904</v>
+        <v>-0.0002459002731658833</v>
       </c>
       <c r="CL3" t="n">
-        <v>-0.0002150093068071457</v>
+        <v>-2.050338953828994e-05</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.0001043554955056492</v>
+        <v>8.834939372317386e-05</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.000115494256830766</v>
+        <v>9.276564219322881e-05</v>
       </c>
       <c r="CO3" t="n">
-        <v>4.354713687866885e-05</v>
+        <v>0.000347261576216632</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.046572475144059e-05</v>
+        <v>-4.116234119611817e-05</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.0005473913261356556</v>
+        <v>-0.0001349049900962396</v>
       </c>
       <c r="CR3" t="n">
-        <v>-0.001385217464031354</v>
+        <v>-0.001161538982956739</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.0001549552771386264</v>
+        <v>-0.0006826139697661026</v>
       </c>
       <c r="CT3" t="n">
-        <v>-3.19260383641451e-05</v>
+        <v>-0.002486142905431069</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.775733405843027e-05</v>
+        <v>1.077302858070506e-05</v>
       </c>
       <c r="CV3" t="n">
-        <v>-5.86510263925758e-07</v>
+        <v>1.075268817204433e-05</v>
       </c>
       <c r="CW3" t="n">
         <v>0</v>
       </c>
       <c r="CX3" t="n">
-        <v>-0.0002289295166049121</v>
+        <v>-0.000746070708763469</v>
       </c>
       <c r="CY3" t="n">
-        <v>8.41607947651002e-05</v>
+        <v>-0.0008432710146049382</v>
       </c>
       <c r="CZ3" t="n">
-        <v>3.763440860215184e-05</v>
+        <v>5.997692741053218e-06</v>
       </c>
       <c r="DA3" t="n">
-        <v>-0.0001075268817204233</v>
+        <v>-5.376344086021057e-06</v>
       </c>
       <c r="DB3" t="n">
-        <v>5.800247770716749e-05</v>
+        <v>0.0003359137392376899</v>
       </c>
       <c r="DC3" t="n">
-        <v>-0.0006827294535806449</v>
+        <v>-0.001055993345346117</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.139159141930526e-05</v>
+        <v>6.591455669036738e-05</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.0001497071115300652</v>
+        <v>1.452236140834007e-05</v>
       </c>
       <c r="DF3" t="n">
-        <v>-9.257370932296948e-05</v>
+        <v>-0.0003701217781236287</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.0001143514313685123</v>
+        <v>-0.0001811399711453654</v>
       </c>
       <c r="DH3" t="n">
-        <v>-0.003544895883680613</v>
+        <v>-0.003401559834360616</v>
       </c>
       <c r="DI3" t="n">
-        <v>1.586724080558937e-06</v>
+        <v>-0.0001795071879504917</v>
       </c>
       <c r="DJ3" t="n">
-        <v>-0.0001052491320592275</v>
+        <v>-0.0003377601821196929</v>
       </c>
       <c r="DK3" t="n">
-        <v>0.0001747202924601354</v>
+        <v>-0.0005529525873158514</v>
       </c>
       <c r="DL3" t="n">
-        <v>2.856752323674438e-05</v>
+        <v>3.324099722991525e-05</v>
       </c>
       <c r="DM3" t="n">
-        <v>-3.323713612480294e-05</v>
+        <v>-0.0002658683522135885</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.0009332657237666709</v>
+        <v>0.0001439735241058304</v>
       </c>
       <c r="DO3" t="n">
-        <v>-0.0008362974009369428</v>
+        <v>-0.002414548649013303</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.000399615465652331</v>
+        <v>-0.0006250109468459964</v>
       </c>
       <c r="DQ3" t="n">
-        <v>4.237288135593431e-05</v>
+        <v>-4.961682674919912e-07</v>
       </c>
       <c r="DR3" t="n">
-        <v>0</v>
+        <v>-5.376344086021057e-06</v>
       </c>
       <c r="DS3" t="n">
-        <v>4.490747347890345e-05</v>
+        <v>3.193625188527394e-05</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.0009756743466422368</v>
+        <v>-0.0007587838292259708</v>
       </c>
       <c r="DU3" t="n">
-        <v>-0.003306591839709523</v>
+        <v>-0.003567468918990346</v>
       </c>
       <c r="DV3" t="n">
         <v>0</v>
       </c>
       <c r="DW3" t="n">
-        <v>0</v>
+        <v>1.526814199625304e-05</v>
       </c>
       <c r="DX3" t="n">
-        <v>8.577289140443756e-05</v>
+        <v>-0.0001761550122064293</v>
       </c>
       <c r="DY3" t="n">
-        <v>-0.0002970852161176728</v>
+        <v>0.0001397309851892759</v>
       </c>
       <c r="DZ3" t="n">
-        <v>-3.796205284007703e-05</v>
+        <v>-5.452153022904803e-05</v>
       </c>
       <c r="EA3" t="n">
-        <v>-9.168468025069765e-05</v>
+        <v>-0.00127325442354483</v>
       </c>
       <c r="EB3" t="n">
-        <v>-0.0015761416846656</v>
+        <v>-0.002135273036999834</v>
       </c>
       <c r="EC3" t="n">
-        <v>-0.0003176981743456286</v>
+        <v>-0.001282986907439805</v>
       </c>
       <c r="ED3" t="n">
-        <v>0.0001931394110863971</v>
+        <v>-0.0002453720115317948</v>
       </c>
       <c r="EE3" t="n">
-        <v>0</v>
+        <v>-6.0606060606061e-06</v>
       </c>
       <c r="EF3" t="n">
-        <v>-5.31884307975461e-06</v>
+        <v>-7.119882918202314e-05</v>
       </c>
       <c r="EG3" t="n">
-        <v>5.296062614892684e-05</v>
+        <v>-0.0004774758996278883</v>
       </c>
       <c r="EH3" t="n">
-        <v>4.709576138147931e-05</v>
+        <v>0</v>
       </c>
       <c r="EI3" t="n">
-        <v>-9.342775305850814e-05</v>
+        <v>-0.0003515521874902005</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.0002014573332919667</v>
+        <v>1.660090043579809e-05</v>
       </c>
       <c r="EK3" t="n">
-        <v>2.645127529920521e-05</v>
+        <v>-9.54880658954038e-05</v>
       </c>
       <c r="EL3" t="n">
-        <v>0</v>
+        <v>-0.0001182795698924688</v>
       </c>
       <c r="EM3" t="n">
-        <v>3.040965302408382e-05</v>
+        <v>4.266945112911146e-05</v>
       </c>
       <c r="EN3" t="n">
-        <v>1.701101540655947e-05</v>
+        <v>-1.21212121212122e-05</v>
       </c>
       <c r="EO3" t="n">
         <v>0</v>
       </c>
       <c r="EP3" t="n">
-        <v>4.83870967741995e-05</v>
+        <v>0</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.0004259304521869134</v>
+        <v>-5.338803992627217e-06</v>
       </c>
       <c r="ER3" t="n">
-        <v>1.368523949170086e-06</v>
+        <v>0</v>
       </c>
       <c r="ES3" t="n">
-        <v>1.16346713205373e-05</v>
+        <v>-8.063687724705338e-06</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.0001112786105151465</v>
+        <v>0.0001301386306403862</v>
       </c>
       <c r="EU3" t="n">
-        <v>0.0001164259618103869</v>
+        <v>6.987145109036972e-05</v>
       </c>
       <c r="EV3" t="n">
-        <v>0</v>
+        <v>-1.645667649599281e-05</v>
       </c>
       <c r="EW3" t="n">
-        <v>-0.0001278955663868564</v>
+        <v>-6.405762499346434e-05</v>
       </c>
       <c r="EX3" t="n">
-        <v>0.0001032907820894668</v>
+        <v>-0.000487810297025606</v>
       </c>
       <c r="EY3" t="n">
-        <v>2.42424242424244e-05</v>
+        <v>-1.18994430047914e-05</v>
       </c>
     </row>
     <row r="4">
@@ -2145,466 +2145,466 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001335632004649232</v>
+        <v>0.00230881354233934</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0007339472434287161</v>
+        <v>0.001088409560170521</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001003117565606708</v>
+        <v>0.002886809103708731</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00135558810547577</v>
+        <v>0.001221837688371474</v>
       </c>
       <c r="F4" t="n">
-        <v>9.402992592711749e-05</v>
+        <v>0.0006556587193912144</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001634017502273722</v>
+        <v>0.002151718747422473</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0004179531520316634</v>
+        <v>0.0003166384628575926</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0006907823028610883</v>
+        <v>0.0009806040367000696</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002136625564903542</v>
+        <v>0.001075887028348447</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0002822961547307135</v>
+        <v>0.0003766259976258049</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0004022866528073158</v>
+        <v>0.0002580408753720699</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0003531490179783096</v>
+        <v>0.0002569756255145565</v>
       </c>
       <c r="N4" t="n">
-        <v>0.000762996707470057</v>
+        <v>0.001973103422979472</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0009588638648222236</v>
+        <v>0.0007292903694110279</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0005278933438084445</v>
+        <v>0.001356878078511665</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.002891658731049111</v>
+        <v>0.002862836201944044</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0006144253034541877</v>
+        <v>0.001165551392709918</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0004901979249953293</v>
+        <v>0.001003399684283331</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0005021991050489119</v>
+        <v>0.0005172953885334322</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0004514076972532034</v>
+        <v>0.0006990329224356127</v>
       </c>
       <c r="V4" t="n">
-        <v>0.000618265767570525</v>
+        <v>0.001621132771015044</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0006467012947185589</v>
+        <v>0.0005455346536021772</v>
       </c>
       <c r="X4" t="n">
-        <v>0.001724456422341806</v>
+        <v>0.001890343452154715</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0002206312616768475</v>
+        <v>0.00066884337571444</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0008241858137111703</v>
+        <v>0.00200837442628314</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.001017929071958978</v>
+        <v>0.0009176789977740168</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.939105453715199e-05</v>
+        <v>0.0005570201356545282</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.002852965585176511</v>
+        <v>0.003852645508982885</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.004763473269357162</v>
+        <v>0.004960374276677966</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.009339437319048923</v>
+        <v>0.01376664811171854</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.002640204945625793</v>
+        <v>0.004041091421072426</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.0006348129278678271</v>
+        <v>0.0007252669181793068</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.001240756345590306</v>
+        <v>0.0005295986646069268</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.0005909097198705893</v>
+        <v>0.0007094264068686401</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.006375404974851378</v>
+        <v>0.004439519877422936</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.01901512117448532</v>
+        <v>0.01971168840585319</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.00103849644137446</v>
+        <v>0.0006375847868342571</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.008556099818544282</v>
+        <v>0.005909818953349031</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.001242153897554342</v>
+        <v>0.002016465768343956</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.001928666248721068</v>
+        <v>0.0009663647048242063</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.0001851645125208401</v>
+        <v>0.0006570908330390419</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.0009696351848477847</v>
+        <v>0.001220898300204914</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.01452367278452198</v>
+        <v>0.01071072019387384</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.0005320152903094555</v>
+        <v>0.0005408582009700659</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.001011060093035799</v>
+        <v>0.00143804073553186</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.0003808871298359412</v>
+        <v>0.0003611093402638814</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.00205225163914658</v>
+        <v>0.001199284024421895</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.001846732680317974</v>
+        <v>0.001273745597543237</v>
       </c>
       <c r="AX4" t="n">
-        <v>3.367762698963763e-05</v>
+        <v>0.0004082970583513552</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.00203641106689346</v>
+        <v>0.001694536117794297</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.0007642498554381661</v>
+        <v>0.0009764840329417664</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.001626118401533586</v>
+        <v>0.00303524983303773</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.002279227068346215</v>
+        <v>0.00520377204146347</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.0003146092716157982</v>
+        <v>0.0005272720670314237</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.0003685113722235582</v>
+        <v>0.0003451218872872316</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.001208521798043983</v>
+        <v>0.0009145164891471687</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.005363400866609381</v>
+        <v>0.004990740851452194</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.000690460006686348</v>
+        <v>0.0006368454789465252</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.0006002408089063603</v>
+        <v>0.0007334742863721641</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.00516622198214984</v>
+        <v>0.007617321969906595</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.001053960850187487</v>
+        <v>0.001651967385827208</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.001224743534060615</v>
+        <v>0.0009210040166260559</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.0004946551744660118</v>
+        <v>8.077063677657716e-05</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.001351916912038671</v>
+        <v>0.001262086701590538</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.001214958203343019</v>
+        <v>0.001674971078259986</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.002135425904071678</v>
+        <v>0.002744134465182176</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.00898723255226635</v>
+        <v>0.00947491125087712</v>
       </c>
       <c r="BQ4" t="n">
         <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.00299276376063485</v>
+        <v>0.003244695829339731</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.004168875010323754</v>
+        <v>0.002057985890152863</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.000256748237603692</v>
+        <v>0.0005113569481850265</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.004255223547477344</v>
+        <v>0.01188556935292413</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.0007989402173086348</v>
+        <v>0.0002770799570923165</v>
       </c>
       <c r="BW4" t="n">
-        <v>4.270469817572317e-05</v>
+        <v>4.788611141118671e-05</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.002316889963623928</v>
+        <v>0.009110514937321788</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.001389339172778666</v>
+        <v>0.001330249917673503</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.003052148357341715</v>
+        <v>0.002280517521656796</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.001115941676386541</v>
+        <v>0.001507261055895982</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.0001806480459479584</v>
+        <v>0.005774716114869248</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.0006991411341027362</v>
+        <v>0.0008447367196429752</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.001839685740135677</v>
+        <v>0.002075959840567036</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.0007180262075596242</v>
+        <v>0.003008783400479075</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.001414851074163218</v>
+        <v>0.004175281772298771</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.002361360801323341</v>
+        <v>0.01083565667444222</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.0006232012789644203</v>
+        <v>0.00101412821923918</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.002141758335428645</v>
+        <v>0.009556325397636865</v>
       </c>
       <c r="CJ4" t="n">
-        <v>3.400298559320554e-05</v>
+        <v>0.0001564995272782704</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.0006726279111468596</v>
+        <v>0.0007138080898712071</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.001557004174543334</v>
+        <v>0.001943980013257584</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.0002454570058237874</v>
+        <v>0.0005560636142852319</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.000150302956949694</v>
+        <v>0.0001776811555482214</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.0001054394430872645</v>
+        <v>0.0007164568501946993</v>
       </c>
       <c r="CP4" t="n">
-        <v>3.309552757895183e-05</v>
+        <v>0.0001500118687988404</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.0007908822872832054</v>
+        <v>0.0009428406378391759</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.005598189128154262</v>
+        <v>0.002604473984442704</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.000479911354185914</v>
+        <v>0.003065605606333585</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.0003973803287437488</v>
+        <v>0.005946568558808454</v>
       </c>
       <c r="CU4" t="n">
-        <v>3.840264110681955e-05</v>
+        <v>2.272308560375847e-05</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.0002013760107263341</v>
+        <v>3.400298559321256e-05</v>
       </c>
       <c r="CW4" t="n">
         <v>0</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.001422898635379067</v>
+        <v>0.002730784999924895</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.0002989425492546492</v>
+        <v>0.002623062160506486</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.0001190104495762334</v>
+        <v>4.262809094961923e-05</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.0003400298559320624</v>
+        <v>1.700149279660277e-05</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.0001837765071955248</v>
+        <v>0.0008210801727271134</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.001983095966077609</v>
+        <v>0.003631058077857885</v>
       </c>
       <c r="DD4" t="n">
-        <v>7.649067431403746e-05</v>
+        <v>0.0003291992864439781</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.0005008787732212324</v>
+        <v>0.0001240076908734898</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.0007798318791704609</v>
+        <v>0.001561703778723861</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.0004473561093723912</v>
+        <v>0.000860411406427628</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.01441692459446969</v>
+        <v>0.01374549242688483</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.0004236564058100001</v>
+        <v>0.002236323418153304</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.0004495525450648455</v>
+        <v>0.0007783002661490479</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.0007757611276206745</v>
+        <v>0.0006995055026673008</v>
       </c>
       <c r="DL4" t="n">
-        <v>6.918130704863226e-05</v>
+        <v>0.00010511726294188</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.0004282055042721751</v>
+        <v>0.000859619928771261</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.001850343725156435</v>
+        <v>0.0007392390869505222</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.004371511998783364</v>
+        <v>0.01167478852727574</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.003431362232958191</v>
+        <v>0.003034777964327446</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.0001339948161088363</v>
+        <v>6.427822506819363e-05</v>
       </c>
       <c r="DR4" t="n">
-        <v>0</v>
+        <v>1.700149279660277e-05</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.0002032478536868677</v>
+        <v>0.0001869008342138289</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.001304102057032082</v>
+        <v>0.003104518979189958</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.01609461262882896</v>
+        <v>0.0138621777590371</v>
       </c>
       <c r="DV4" t="n">
         <v>0</v>
       </c>
       <c r="DW4" t="n">
-        <v>0</v>
+        <v>0.000116553116967509</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.0006785291936073621</v>
+        <v>0.0005827908206840011</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.00558805548626724</v>
+        <v>0.006294853622521551</v>
       </c>
       <c r="DZ4" t="n">
-        <v>8.827286697851094e-05</v>
+        <v>0.0001991502459545867</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.0003210196928473885</v>
+        <v>0.003609245971018892</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.006959616664856511</v>
+        <v>0.01045529343433725</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.0009065036998478023</v>
+        <v>0.004334663618447931</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.0002276224749385334</v>
+        <v>0.000554444798775623</v>
       </c>
       <c r="EE4" t="n">
-        <v>0</v>
+        <v>1.916531915253576e-05</v>
       </c>
       <c r="EF4" t="n">
-        <v>3.950570916147528e-05</v>
+        <v>0.0001197803554473332</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.0005223492618087369</v>
+        <v>0.001066488413847805</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.0001489298741052727</v>
+        <v>0</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.0003359836208791594</v>
+        <v>0.0004480701045617681</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.00050469871172348</v>
+        <v>0.0002864643862906879</v>
       </c>
       <c r="EK4" t="n">
-        <v>5.696967460547653e-05</v>
+        <v>0.0007125496249539174</v>
       </c>
       <c r="EL4" t="n">
-        <v>0</v>
+        <v>0.0003740328415252786</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.0001610217448969014</v>
+        <v>0.0001401203109374029</v>
       </c>
       <c r="EN4" t="n">
-        <v>3.87775977641184e-05</v>
+        <v>3.833063830507151e-05</v>
       </c>
       <c r="EO4" t="n">
         <v>0</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.0001530134351694565</v>
+        <v>0</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.0007467327321247395</v>
+        <v>0.0005353229073085224</v>
       </c>
       <c r="ER4" t="n">
-        <v>5.399143969522193e-05</v>
+        <v>0</v>
       </c>
       <c r="ES4" t="n">
-        <v>3.679206120033685e-05</v>
+        <v>5.052219696809692e-05</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.000550034806734069</v>
+        <v>0.0007474960511030861</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.0005841981927958131</v>
+        <v>0.0009728996037199968</v>
       </c>
       <c r="EV4" t="n">
-        <v>0</v>
+        <v>3.720761898043461e-05</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.0004057670984291376</v>
+        <v>0.0002909382360885775</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.0002291931571384456</v>
+        <v>0.0009184100610472937</v>
       </c>
       <c r="EY4" t="n">
-        <v>7.666127661014302e-05</v>
+        <v>0.0001567888125354473</v>
       </c>
     </row>
     <row r="5">
@@ -2614,466 +2614,466 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>-0.004354838709677389</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.00266875981161695</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.00870967741935481</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.001936159079016209</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-0.002043010752688146</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-0.0007062146892655718</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.0008372579801150803</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-0.0007526881720429479</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-0.002152414194298991</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-0.0008864265927978066</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-0.0006094182825484795</v>
+      </c>
+      <c r="M5" t="n">
+        <v>-0.0004943502824859003</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-0.002675974403723069</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-0.002150537634408567</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-0.001075268817204278</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-0.003601694915254305</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-0.003035060177917304</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-0.0001745200698080263</v>
+      </c>
+      <c r="T5" t="n">
         <v>-0.0005913978494623163</v>
       </c>
-      <c r="C5" t="n">
-        <v>-0.002085561497326227</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-0.0007486631016043078</v>
-      </c>
-      <c r="F5" t="n">
-        <v>-0.0002688172043010306</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-0.0007849293563578996</v>
-      </c>
-      <c r="I5" t="n">
-        <v>-0.0006951871657754349</v>
-      </c>
-      <c r="J5" t="n">
-        <v>-0.002094240837696315</v>
-      </c>
-      <c r="K5" t="n">
-        <v>-0.0002770083102492937</v>
-      </c>
-      <c r="L5" t="n">
-        <v>-0.0006355932203389147</v>
-      </c>
-      <c r="M5" t="n">
-        <v>-0.000909090909090926</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-0.001129943502824815</v>
-      </c>
-      <c r="O5" t="n">
-        <v>-0.0004278074866310488</v>
-      </c>
-      <c r="P5" t="n">
-        <v>-0.0001075847229693228</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>-0.001163467132053508</v>
-      </c>
-      <c r="R5" t="n">
-        <v>-0.001836158192090376</v>
-      </c>
-      <c r="S5" t="n">
-        <v>-0.0008021390374332027</v>
-      </c>
-      <c r="T5" t="n">
-        <v>-0.0001069518716577678</v>
-      </c>
       <c r="U5" t="n">
-        <v>-0.0009139784946236129</v>
+        <v>-0.001098901098901039</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.0007486631016043078</v>
+        <v>-0.0002673796791444194</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.00149732620320856</v>
+        <v>-0.001612903225806406</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.00299465240641712</v>
+        <v>-0.001059322033898358</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.0006951871657754349</v>
+        <v>-0.001831501831501814</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>-0.004569892473118254</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.001978609625668493</v>
+        <v>-0.0008455467869222799</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>-0.001495844875346286</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.003319209039547966</v>
+        <v>-0.00748587570621474</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.00494350282485877</v>
+        <v>-0.0024011299435029</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.0006802721088434938</v>
+        <v>0.000394588500563664</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.003689839572192532</v>
+        <v>-0.006344086021505347</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>-0.000303030303030305</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.0002326934264107017</v>
+        <v>-0.000169109357384456</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.001497326203208593</v>
+        <v>-0.002096774193548345</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.003582887700534776</v>
+        <v>-0.0008864265927978066</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.0009180790960451434</v>
+        <v>-0.0004943502824859114</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.0003324099722991525</v>
+        <v>-0.001108033240997241</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.003248587570621442</v>
+        <v>-0.0007768361581921401</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.00254237288135587</v>
+        <v>-0.0002673796791444194</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.000645161290322549</v>
+        <v>-0.0009307737056428067</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>-0.001666666666666639</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.002673796791443839</v>
+        <v>-0.001014656144306736</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.0005073280721533679</v>
+        <v>-0.0004509582863585493</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0.0008474576271185974</v>
+        <v>-0.000666666666666671</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0.0008474576271185863</v>
+        <v>-0.002688172043010728</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.0008021390374331805</v>
+        <v>-0.0009419152276294751</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.0001046572475143725</v>
+        <v>-0.0006355932203390147</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.0007062146892654608</v>
+        <v>-0.0006355932203390147</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.00346045197740108</v>
+        <v>-0.004590395480226039</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.00149732620320856</v>
+        <v>-0.000484848484848488</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0.001279813845258859</v>
+        <v>-0.003664921465968551</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0.0019067796610169</v>
+        <v>-0.0040443213296399</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0.0001612903225806317</v>
+        <v>-0.001570680628272236</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.0002326934264107017</v>
+        <v>-0.001047120418848157</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.003723094822571227</v>
+        <v>-0.002326934264107017</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.004421175101803332</v>
+        <v>-0.003781268179173902</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.0008021390374331916</v>
+        <v>-0.001182795698924677</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>-0.0005649717514124575</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0.00254237288135587</v>
+        <v>-0.001624293785310815</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-0.0009418282548476764</v>
+        <v>-0.005337519623233899</v>
       </c>
       <c r="BK5" t="n">
-        <v>-0.001451612903225752</v>
+        <v>-0.0005913978494623273</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0.001129943502824804</v>
+        <v>-0.0002093144950287673</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.0007272727272726875</v>
+        <v>-0.0008726003490401313</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0.002501454333915043</v>
+        <v>-0.003781268179173902</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0.002754237288135519</v>
+        <v>-0.008763440860215011</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0.02827956989247308</v>
+        <v>-0.02978494623655913</v>
       </c>
       <c r="BQ5" t="n">
         <v>0</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0.008225806451612838</v>
+        <v>-0.009784946236559112</v>
       </c>
       <c r="BS5" t="n">
-        <v>-0.01274193548387093</v>
+        <v>-0.006505376344086012</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0.000181818181818183</v>
+        <v>-0.001129032258064477</v>
       </c>
       <c r="BU5" t="n">
-        <v>-0.01327956989247308</v>
+        <v>-0.03731182795698922</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.002526881720430063</v>
+        <v>-0.000666666666666671</v>
       </c>
       <c r="BW5" t="n">
-        <v>-7.062146892654609e-05</v>
+        <v>-5.540166204985875e-05</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.006720430107526843</v>
+        <v>-0.02876344086021504</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.002419354838709631</v>
+        <v>-0.0004432132963989033</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-5.347593582888388e-05</v>
+        <v>-0.001828254847645439</v>
       </c>
       <c r="CA5" t="n">
-        <v>-0.000424242424242427</v>
+        <v>-0.002956989247311781</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0.0001604278074866516</v>
+        <v>-0.01844086021505372</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0.001182795698924688</v>
+        <v>-0.00188172043010747</v>
       </c>
       <c r="CD5" t="n">
-        <v>-0.004193548387096724</v>
+        <v>-0.00387096774193546</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.001989247311827924</v>
+        <v>-0.008494623655913946</v>
       </c>
       <c r="CF5" t="n">
-        <v>-0.004032258064516081</v>
+        <v>-0.01252688172043007</v>
       </c>
       <c r="CG5" t="n">
-        <v>-0.007419354838709635</v>
+        <v>-0.03387096774193547</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.0001075847229693228</v>
+        <v>-0.002564102564102533</v>
       </c>
       <c r="CI5" t="n">
-        <v>-0.00612903225806446</v>
+        <v>-0.02999999999999998</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0.0001075268817204211</v>
+        <v>-0.0001127395715896373</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0.0002216066481994461</v>
+        <v>-0.002096774193548345</v>
       </c>
       <c r="CL5" t="n">
-        <v>-0.004301075268817156</v>
+        <v>-0.002956989247311792</v>
       </c>
       <c r="CM5" t="n">
-        <v>0</v>
+        <v>-0.0004986149584487621</v>
       </c>
       <c r="CN5" t="n">
-        <v>0</v>
+        <v>-5.636978579481866e-05</v>
       </c>
       <c r="CO5" t="n">
-        <v>-5.347593582888388e-05</v>
+        <v>0</v>
       </c>
       <c r="CP5" t="n">
-        <v>0</v>
+        <v>-0.0004653868528214034</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0</v>
+        <v>-0.001989247311827913</v>
       </c>
       <c r="CR5" t="n">
-        <v>-0.01715053763440857</v>
+        <v>-0.008333333333333314</v>
       </c>
       <c r="CS5" t="n">
-        <v>-0.0004943502824858226</v>
+        <v>-0.008924731182795664</v>
       </c>
       <c r="CT5" t="n">
-        <v>-0.0005649717514123687</v>
+        <v>-0.0187096774193548</v>
       </c>
       <c r="CU5" t="n">
         <v>0</v>
       </c>
       <c r="CV5" t="n">
-        <v>-0.0004301075268816845</v>
+        <v>0</v>
       </c>
       <c r="CW5" t="n">
         <v>0</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0.002419354838709631</v>
+        <v>-0.008172043010752684</v>
       </c>
       <c r="CY5" t="n">
-        <v>-0.0005376344086021057</v>
+        <v>-0.007258064516128981</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0</v>
+        <v>-5.636978579481866e-05</v>
       </c>
       <c r="DA5" t="n">
-        <v>-0.001075268817204233</v>
+        <v>-5.376344086021057e-05</v>
       </c>
       <c r="DB5" t="n">
+        <v>-0.0005540166204986097</v>
+      </c>
+      <c r="DC5" t="n">
+        <v>-0.01069892473118277</v>
+      </c>
+      <c r="DD5" t="n">
+        <v>-0.0004301075268816734</v>
+      </c>
+      <c r="DE5" t="n">
+        <v>-0.0002254791431792746</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>-0.004516129032258042</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>-0.001883656509695308</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>-0.04241935483870966</v>
+      </c>
+      <c r="DI5" t="n">
+        <v>-0.004354838709677389</v>
+      </c>
+      <c r="DJ5" t="n">
+        <v>-0.00198848770277339</v>
+      </c>
+      <c r="DK5" t="n">
+        <v>-0.002150537634408545</v>
+      </c>
+      <c r="DL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM5" t="n">
+        <v>-0.002258064516128977</v>
+      </c>
+      <c r="DN5" t="n">
+        <v>-0.0009307737056428067</v>
+      </c>
+      <c r="DO5" t="n">
+        <v>-0.0351075268817204</v>
+      </c>
+      <c r="DP5" t="n">
+        <v>-0.008655913978494601</v>
+      </c>
+      <c r="DQ5" t="n">
+        <v>-0.0001569858712715755</v>
+      </c>
+      <c r="DR5" t="n">
         <v>-5.376344086021057e-05</v>
-      </c>
-      <c r="DC5" t="n">
-        <v>-0.006290322580645102</v>
-      </c>
-      <c r="DD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="DE5" t="n">
-        <v>-0.0004301075268816734</v>
-      </c>
-      <c r="DF5" t="n">
-        <v>-0.002043010752688124</v>
-      </c>
-      <c r="DG5" t="n">
-        <v>-0.000363636363636366</v>
-      </c>
-      <c r="DH5" t="n">
-        <v>-0.04419354838709674</v>
-      </c>
-      <c r="DI5" t="n">
-        <v>-0.0005649717514123687</v>
-      </c>
-      <c r="DJ5" t="n">
-        <v>-0.0008349705304518728</v>
-      </c>
-      <c r="DK5" t="n">
-        <v>-0.0009823182711198308</v>
-      </c>
-      <c r="DL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM5" t="n">
-        <v>-0.0009090909090909482</v>
-      </c>
-      <c r="DN5" t="n">
-        <v>-0.00182795698924727</v>
-      </c>
-      <c r="DO5" t="n">
-        <v>-0.01247311827956983</v>
-      </c>
-      <c r="DP5" t="n">
-        <v>-0.007258064516128959</v>
-      </c>
-      <c r="DQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR5" t="n">
-        <v>0</v>
       </c>
       <c r="DS5" t="n">
         <v>-0.0001569858712715755</v>
       </c>
       <c r="DT5" t="n">
-        <v>-0.0003225806451612412</v>
+        <v>-0.00854838709677418</v>
       </c>
       <c r="DU5" t="n">
-        <v>-0.04827956989247308</v>
+        <v>-0.0429569892473118</v>
       </c>
       <c r="DV5" t="n">
         <v>0</v>
       </c>
       <c r="DW5" t="n">
-        <v>0</v>
+        <v>-0.0001612903225806317</v>
       </c>
       <c r="DX5" t="n">
+        <v>-0.0009090909090909149</v>
+      </c>
+      <c r="DY5" t="n">
+        <v>-0.01532258064516125</v>
+      </c>
+      <c r="DZ5" t="n">
+        <v>-0.0005913978494623384</v>
+      </c>
+      <c r="EA5" t="n">
+        <v>-0.01150537634408599</v>
+      </c>
+      <c r="EB5" t="n">
+        <v>-0.03102150537634405</v>
+      </c>
+      <c r="EC5" t="n">
+        <v>-0.01360215053763437</v>
+      </c>
+      <c r="ED5" t="n">
+        <v>-0.001465201465201438</v>
+      </c>
+      <c r="EE5" t="n">
+        <v>-6.0606060606061e-05</v>
+      </c>
+      <c r="EF5" t="n">
+        <v>-0.0003208556149733033</v>
+      </c>
+      <c r="EG5" t="n">
+        <v>-0.003333333333333321</v>
+      </c>
+      <c r="EH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI5" t="n">
+        <v>-0.001182795698924677</v>
+      </c>
+      <c r="EJ5" t="n">
+        <v>-0.0005073280721533679</v>
+      </c>
+      <c r="EK5" t="n">
+        <v>-0.001720430107526827</v>
+      </c>
+      <c r="EL5" t="n">
+        <v>-0.001182795698924688</v>
+      </c>
+      <c r="EM5" t="n">
+        <v>-0.0001604278074866516</v>
+      </c>
+      <c r="EN5" t="n">
+        <v>-0.000121212121212122</v>
+      </c>
+      <c r="EO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ5" t="n">
+        <v>-0.0006355932203390147</v>
+      </c>
+      <c r="ER5" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES5" t="n">
+        <v>-0.0001412429378531144</v>
+      </c>
+      <c r="ET5" t="n">
+        <v>-0.0007367387033398676</v>
+      </c>
+      <c r="EU5" t="n">
         <v>-0.0009823182711198308</v>
       </c>
-      <c r="DY5" t="n">
-        <v>-0.01526881720430103</v>
-      </c>
-      <c r="DZ5" t="n">
-        <v>-0.0002688172043010528</v>
-      </c>
-      <c r="EA5" t="n">
-        <v>-0.0009823182711198308</v>
-      </c>
-      <c r="EB5" t="n">
-        <v>-0.02112903225806446</v>
-      </c>
-      <c r="EC5" t="n">
-        <v>-0.002634408602150495</v>
-      </c>
-      <c r="ED5" t="n">
-        <v>0</v>
-      </c>
-      <c r="EE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="EF5" t="n">
-        <v>-0.0001069518716577678</v>
-      </c>
-      <c r="EG5" t="n">
-        <v>-0.0009823182711198308</v>
-      </c>
-      <c r="EH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="EI5" t="n">
-        <v>-0.0009823182711198308</v>
-      </c>
-      <c r="EJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="EK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="EL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="EM5" t="n">
-        <v>-0.0001612903225806317</v>
-      </c>
-      <c r="EN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="EO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="EP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="EQ5" t="n">
-        <v>-5.376344086018836e-05</v>
-      </c>
-      <c r="ER5" t="n">
-        <v>-0.0001075268817204211</v>
-      </c>
-      <c r="ES5" t="n">
-        <v>0</v>
-      </c>
-      <c r="ET5" t="n">
-        <v>-0.0009332023575638448</v>
-      </c>
-      <c r="EU5" t="n">
-        <v>-0.0009332023575638448</v>
-      </c>
       <c r="EV5" t="n">
-        <v>0</v>
+        <v>-0.0001108033240997175</v>
       </c>
       <c r="EW5" t="n">
-        <v>-0.0009823182711198308</v>
+        <v>-0.0008484848484848539</v>
       </c>
       <c r="EX5" t="n">
-        <v>-0.0001163467132053508</v>
+        <v>-0.00274193548387095</v>
       </c>
       <c r="EY5" t="n">
-        <v>0</v>
+        <v>-0.0003878116343490223</v>
       </c>
     </row>
     <row r="6">
@@ -3083,97 +3083,97 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>-0.0002643527984254879</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>-0.0004538652049392134</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-8.326672684688675e-18</v>
+        <v>-0.000249307479224381</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0001615563923256263</v>
+        <v>-8.021390374332582e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0002978941961992748</v>
+        <v>-0.0004163791616353163</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>-0.0003102850539291352</v>
       </c>
       <c r="J6" t="n">
-        <v>-3.683693516699782e-05</v>
+        <v>-0.0005161822827246809</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>-0.0001059322033898358</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-3.924646781788554e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-0.0003208556149733033</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0002016129032257896</v>
+        <v>-0.000463835765431006</v>
       </c>
       <c r="O6" t="n">
-        <v>-8.068854222699208e-05</v>
+        <v>-0.0005926697635617096</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.0002727272727272662</v>
+        <v>-0.0002654045365243718</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.0003663101604278324</v>
+        <v>-0.001776967711511643</v>
       </c>
       <c r="S6" t="n">
-        <v>5.636978579481866e-05</v>
+        <v>1.336898395721264e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-0.0001320965152684317</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>-0.0005712122634865729</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.0004459406140078393</v>
       </c>
       <c r="X6" t="n">
-        <v>4.545454545454575e-05</v>
+        <v>0.0003290860880417801</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>-0.0002727272727272745</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.296610169491789e-05</v>
+        <v>-0.0005831369527780628</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>-0.0004644925711407732</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.000153728198780656</v>
+        <v>-0.0002894144310960356</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.000151150774470532</v>
+        <v>0.0003793957882424953</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.003194272568618137</v>
+        <v>0.003592971600825071</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>-0.0006474041306194112</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -3182,319 +3182,319 @@
         <v>0</v>
       </c>
       <c r="AI6" t="n">
+        <v>-0.0005915750915750889</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>-3.20855614973331e-05</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.004113255080785966</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.0003260352213231871</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>-8.064516129029087e-05</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-0.000163101604278082</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-0.0001486685729603865</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0.003028020204170301</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>-0.0003016361029815729</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>-0.0003054101221640459</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>-0.0001604278074866516</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>-8.310249307480477e-05</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>-0.000969134357543755</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>-0.0004363001745200768</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>-0.0003378115598443893</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>-0.0004145176090877833</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>-0.0009880452768415539</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>-0.0009780006303718558</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>-4.227733934613065e-05</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>-0.0001043499511241441</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>-0.0004090909090909117</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>-0.0001631016042780792</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>-0.001804426511600341</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>-0.0003324099722991608</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>-4.034427111352102e-05</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>-0.0005109152403402761</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>-0.0002868197191759792</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>-0.0001970928231432384</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>-0.0002406417112299497</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>1.515151515151525e-05</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>1.515151515151525e-05</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>-0.0004611845963420347</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>-0.0007156555356001154</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>-0.0002156862745098381</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>-0.0001588983050847537</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>-5.882352941176672e-05</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>-0.0009571308559775614</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>-8.021390374332582e-05</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>-0.0001139980028184606</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>-0.0001731673917021337</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>-0.000542344483412316</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>-4.2277339346114e-05</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>-0.001247739171822934</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>-0.0002133939091815695</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>-0.001019894233190641</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX6" t="n">
+        <v>-0.0007849293563579025</v>
+      </c>
+      <c r="CY6" t="n">
+        <v>-0.0009527209265429215</v>
+      </c>
+      <c r="CZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC6" t="n">
+        <v>-0.001292691311015923</v>
+      </c>
+      <c r="DD6" t="n">
+        <v>-7.849293563578775e-05</v>
+      </c>
+      <c r="DE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF6" t="n">
+        <v>-0.0001604278074866516</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>-0.0006327145803585621</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>0.0001816897791473954</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>-0.0005057815935555987</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>-0.0004606079488867542</v>
+      </c>
+      <c r="DK6" t="n">
+        <v>-0.0008268166719611669</v>
+      </c>
+      <c r="DL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>-0.0004450801299540536</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>-0.0004032258064515792</v>
+      </c>
+      <c r="DO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP6" t="n">
+        <v>-0.000623560012670904</v>
+      </c>
+      <c r="DQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT6" t="n">
+        <v>-0.0005926697635617096</v>
+      </c>
+      <c r="DU6" t="n">
+        <v>6.852916401089981e-05</v>
+      </c>
+      <c r="DV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX6" t="n">
+        <v>-0.0004811089232595323</v>
+      </c>
+      <c r="DY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA6" t="n">
+        <v>-0.0005480578592021835</v>
+      </c>
+      <c r="EB6" t="n">
+        <v>-0.0001059322033898552</v>
+      </c>
+      <c r="EC6" t="n">
+        <v>-7.367387033397065e-05</v>
+      </c>
+      <c r="ED6" t="n">
+        <v>-0.0005241935483870613</v>
+      </c>
+      <c r="EE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF6" t="n">
         <v>-0.0001363636363636373</v>
       </c>
-      <c r="AJ6" t="n">
-        <v>1.22789783889965e-05</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0.003646438204029909</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0.0002091579306418928</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>-0.000362713002602183</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>5.347593582887278e-05</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>-0.0001363636363636373</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0.002719234675264515</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>1.76553672316393e-05</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>-0.0001059322033898191</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>-0.0008206391334265011</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>-0.0002727272727272745</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>-0.0001960055381267617</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>4.614347581134991e-05</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>-4.155124653739407e-05</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>-5.342642705278566e-05</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>-4.545454545454575e-05</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>-0.0002418160664233893</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>-0.0003609625668449495</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>9.823182711197199e-05</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>1.22789783889965e-05</v>
-      </c>
-      <c r="CB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CC6" t="n">
-        <v>-5.890263582571109e-05</v>
-      </c>
-      <c r="CD6" t="n">
-        <v>-0.0001662049861495763</v>
-      </c>
-      <c r="CE6" t="n">
-        <v>-0.0001631016042780847</v>
-      </c>
-      <c r="CF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG6" t="n">
-        <v>-4.363001745200657e-05</v>
-      </c>
-      <c r="CH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL6" t="n">
-        <v>-0.0001480216866399098</v>
-      </c>
-      <c r="CM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR6" t="n">
-        <v>-0.0002908587257617751</v>
-      </c>
-      <c r="CS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT6" t="n">
-        <v>-0.000317596693676217</v>
-      </c>
-      <c r="CU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX6" t="n">
-        <v>-0.0007759859188430308</v>
-      </c>
-      <c r="CY6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC6" t="n">
-        <v>-0.0001813565013010915</v>
-      </c>
-      <c r="DD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH6" t="n">
-        <v>-0.0001588983050847287</v>
-      </c>
-      <c r="DI6" t="n">
-        <v>-0.0001373925259311126</v>
-      </c>
-      <c r="DJ6" t="n">
-        <v>-0.0003487449570398593</v>
-      </c>
-      <c r="DK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DN6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DO6" t="n">
-        <v>-0.0005494505494505141</v>
-      </c>
-      <c r="DP6" t="n">
-        <v>-0.0002946954813359742</v>
-      </c>
-      <c r="DQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX6" t="n">
-        <v>-0.0002077562326869703</v>
-      </c>
-      <c r="DY6" t="n">
-        <v>1.454333915067163e-05</v>
-      </c>
-      <c r="DZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="EA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="EB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="EC6" t="n">
-        <v>-0.0003419793502896007</v>
-      </c>
-      <c r="ED6" t="n">
-        <v>0</v>
-      </c>
-      <c r="EE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="EF6" t="n">
-        <v>0</v>
-      </c>
       <c r="EG6" t="n">
-        <v>0</v>
+        <v>-0.0005455631773511049</v>
       </c>
       <c r="EH6" t="n">
         <v>0</v>
       </c>
       <c r="EI6" t="n">
-        <v>0</v>
+        <v>-0.0005612775485857924</v>
       </c>
       <c r="EJ6" t="n">
         <v>0</v>
@@ -3518,7 +3518,7 @@
         <v>0</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0</v>
+        <v>-0.000418292217178376</v>
       </c>
       <c r="ER6" t="n">
         <v>0</v>
@@ -3530,16 +3530,16 @@
         <v>0</v>
       </c>
       <c r="EU6" t="n">
-        <v>0</v>
+        <v>-0.0003527620539195808</v>
       </c>
       <c r="EV6" t="n">
         <v>0</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0.0003054101221640459</v>
+        <v>0</v>
       </c>
       <c r="EX6" t="n">
-        <v>0</v>
+        <v>-0.0005817174515235501</v>
       </c>
       <c r="EY6" t="n">
         <v>0</v>
@@ -3552,7 +3552,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001400250044650775</v>
+        <v>5.347593582886722e-05</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -3561,22 +3561,22 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0001412429378531144</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0005594941859555225</v>
+        <v>7.941894385902759e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.689618074233069e-05</v>
+        <v>-8.310249307480477e-05</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0003531073446327859</v>
+        <v>2.673796791443639e-05</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -3588,22 +3588,22 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>0.000366684597453798</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-0.0003466021158328947</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0001349602778174253</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.00147849462365594</v>
+        <v>0.0008310775370924839</v>
       </c>
       <c r="R7" t="n">
-        <v>-2.616431187859592e-05</v>
+        <v>-0.0002287968441814669</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0002520336806051293</v>
+        <v>0.0001950869643177144</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -3612,64 +3612,64 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0001108033240997175</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0001187794172087475</v>
+        <v>-6.0606060606061e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0003337611825915743</v>
+        <v>0.0008951048951048646</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0005328022668844134</v>
+        <v>4.940625733445558e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>-0.000133848052400104</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.367387033397898e-05</v>
+        <v>0.0001039769006370261</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.00113901291897362</v>
+        <v>0.001847672502803205</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.01168152794619551</v>
+        <v>0.009667438788317894</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.0001108033240997175</v>
+        <v>-5.379236148467248e-05</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.0001598555054776518</v>
+        <v>2.689618074233069e-05</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>5.379236148466138e-05</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-2.908667830133771e-05</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.0006804331402669229</v>
+        <v>0.0001882443445719029</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.01277166090583399</v>
+        <v>0.0117038756920879</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.000109112635470221</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.002571333428476319</v>
+        <v>0.002545494571337909</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>0.0002087143625605137</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.0002945577534078203</v>
+        <v>0.0001652432209192034</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
@@ -3678,34 +3678,34 @@
         <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.005954814416352911</v>
+        <v>0.00886506519021258</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>-8.455467869224465e-05</v>
       </c>
       <c r="AT7" t="n">
-        <v>5.817335660269762e-05</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
         <v>0</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.0002612371256771995</v>
+        <v>0.0001025918493848588</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.000303030303030305</v>
+        <v>5.347593582887278e-05</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>2.908667830135991e-05</v>
+        <v>0.0001776507709710218</v>
       </c>
       <c r="AZ7" t="n">
-        <v>2.4557956777993e-05</v>
+        <v>5.817335660267542e-05</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.0001565228556754006</v>
+        <v>5.395057431253902e-05</v>
       </c>
       <c r="BB7" t="n">
         <v>0</v>
@@ -3717,112 +3717,112 @@
         <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>-2.673796791444194e-05</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.0001059322033898358</v>
+        <v>0.0008794369854121687</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.0001344086021505542</v>
+        <v>0</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.823182711197199e-05</v>
+        <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.000958460337542627</v>
+        <v>8.302676619132977e-05</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.0002406417112299441</v>
+        <v>-0.0004106981498215201</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.0001515151515151525</v>
+        <v>0</v>
       </c>
       <c r="BL7" t="n">
         <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>2.4557956777993e-05</v>
+        <v>0.0003026200223070763</v>
       </c>
       <c r="BN7" t="n">
-        <v>2.770083102494603e-05</v>
+        <v>8.068854222699206e-05</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>-0.0006864406779661214</v>
       </c>
       <c r="BP7" t="n">
-        <v>6.0606060606061e-05</v>
+        <v>8.053032939909222e-05</v>
       </c>
       <c r="BQ7" t="n">
         <v>0</v>
       </c>
       <c r="BR7" t="n">
-        <v>0</v>
+        <v>0.0001604278074866183</v>
       </c>
       <c r="BS7" t="n">
-        <v>0</v>
+        <v>-2.673796791444749e-05</v>
       </c>
       <c r="BT7" t="n">
-        <v>1.110223024625157e-17</v>
+        <v>0</v>
       </c>
       <c r="BU7" t="n">
-        <v>2.616431187860147e-05</v>
+        <v>-1.110223024625157e-17</v>
       </c>
       <c r="BV7" t="n">
-        <v>0</v>
+        <v>-2.908667830133771e-05</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.0001363759484600158</v>
+        <v>0</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.0001719056974459565</v>
+        <v>0.0001428954574325958</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.0004946070878274367</v>
+        <v>0.0005832861598570383</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.0002537716520767619</v>
+        <v>-8.878667029216247e-05</v>
       </c>
       <c r="CB7" t="n">
-        <v>0</v>
+        <v>-0.0002420656266810262</v>
       </c>
       <c r="CC7" t="n">
         <v>0</v>
       </c>
       <c r="CD7" t="n">
-        <v>0</v>
+        <v>5.379236148466138e-05</v>
       </c>
       <c r="CE7" t="n">
-        <v>0</v>
+        <v>3.531073446327304e-05</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.770083102492937e-05</v>
+        <v>-2.673796791445304e-05</v>
       </c>
       <c r="CG7" t="n">
-        <v>0</v>
+        <v>5.817335660267542e-05</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.0001666890480220562</v>
+        <v>2.455795677799855e-05</v>
       </c>
       <c r="CI7" t="n">
-        <v>0</v>
+        <v>3.03030303030305e-05</v>
       </c>
       <c r="CJ7" t="n">
         <v>0</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.0001412429378531366</v>
+        <v>-5.232862375719183e-05</v>
       </c>
       <c r="CL7" t="n">
-        <v>0</v>
+        <v>-3.531073446327859e-05</v>
       </c>
       <c r="CM7" t="n">
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>6.561376476630909e-05</v>
+        <v>0</v>
       </c>
       <c r="CO7" t="n">
         <v>0</v>
@@ -3831,16 +3831,16 @@
         <v>0</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.000181818181818183</v>
+        <v>0</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-8.197725438208181e-05</v>
       </c>
       <c r="CS7" t="n">
-        <v>0</v>
+        <v>9.823182711199419e-05</v>
       </c>
       <c r="CT7" t="n">
-        <v>0</v>
+        <v>-5.347593582888388e-05</v>
       </c>
       <c r="CU7" t="n">
         <v>0</v>
@@ -3852,22 +3852,22 @@
         <v>0</v>
       </c>
       <c r="CX7" t="n">
-        <v>-8.117676685381325e-05</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
+        <v>-2.818489289740933e-05</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB7" t="n">
         <v>2.673796791443639e-05</v>
       </c>
-      <c r="CZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB7" t="n">
-        <v>0</v>
-      </c>
       <c r="DC7" t="n">
-        <v>0</v>
+        <v>-2.818489289740933e-05</v>
       </c>
       <c r="DD7" t="n">
         <v>0</v>
@@ -3879,19 +3879,19 @@
         <v>0</v>
       </c>
       <c r="DG7" t="n">
-        <v>0</v>
+        <v>-2.673796791444194e-05</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.0003333333333333355</v>
+        <v>0.0003627933350043466</v>
       </c>
       <c r="DI7" t="n">
-        <v>0</v>
+        <v>-2.455795677797634e-05</v>
       </c>
       <c r="DJ7" t="n">
         <v>0</v>
       </c>
       <c r="DK7" t="n">
-        <v>0</v>
+        <v>-0.0003446927909118436</v>
       </c>
       <c r="DL7" t="n">
         <v>0</v>
@@ -3900,13 +3900,13 @@
         <v>0</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.0005068166934571571</v>
+        <v>0.0001348627214306009</v>
       </c>
       <c r="DO7" t="n">
-        <v>0</v>
+        <v>0.0001984938138784087</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.0001344809037116812</v>
+        <v>0.0002572706876016462</v>
       </c>
       <c r="DQ7" t="n">
         <v>0</v>
@@ -3918,10 +3918,10 @@
         <v>0</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.0005046224961479384</v>
+        <v>-1.714553309768439e-05</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.0004273977495981241</v>
+        <v>0.0006942850121168243</v>
       </c>
       <c r="DV7" t="n">
         <v>0</v>
@@ -3930,25 +3930,25 @@
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>0</v>
+        <v>-0.0003820344556861088</v>
       </c>
       <c r="DY7" t="n">
-        <v>0.0003715889716541798</v>
+        <v>0.0005589648446791163</v>
       </c>
       <c r="DZ7" t="n">
         <v>0</v>
       </c>
       <c r="EA7" t="n">
-        <v>0</v>
+        <v>-5.347593582888388e-05</v>
       </c>
       <c r="EB7" t="n">
-        <v>9.09090909090915e-05</v>
+        <v>0.0002852049910873344</v>
       </c>
       <c r="EC7" t="n">
-        <v>-8.053032939911442e-05</v>
+        <v>0</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.0001304901601678288</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
         <v>0</v>
@@ -3963,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0</v>
+        <v>-0.0001163467132053508</v>
       </c>
       <c r="EJ7" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
         <v>0</v>
       </c>
       <c r="EQ7" t="n">
-        <v>6.0606060606061e-05</v>
+        <v>0</v>
       </c>
       <c r="ER7" t="n">
         <v>0</v>
@@ -3999,7 +3999,7 @@
         <v>0</v>
       </c>
       <c r="EU7" t="n">
-        <v>0</v>
+        <v>-2.673796791444194e-05</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
@@ -4021,361 +4021,361 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001753145881792159</v>
+        <v>0.001284292630446465</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>4.155124653739407e-05</v>
+        <v>0.0001813565013010915</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0005120577502777002</v>
+        <v>5.99978846052146e-05</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00203307662170796</v>
+        <v>0.001001387458726708</v>
       </c>
       <c r="H8" t="n">
-        <v>8.726003490402978e-05</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0002794354719437203</v>
+        <v>0.0002014840363256332</v>
       </c>
       <c r="J8" t="n">
-        <v>0.00109911517054376</v>
+        <v>0.0001609215931416358</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0003208556149732533</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>8.882538548549424e-05</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0002308377896613034</v>
+        <v>0.001022892888547258</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0006570301633877119</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0008945432341464776</v>
+        <v>0.0002563594055740665</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.003644611301760253</v>
+        <v>0.001632250533349394</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>-5.347593582888388e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0004444365821984042</v>
+        <v>0.001693294929496197</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>3.68369351669895e-05</v>
+        <v>5.882352941176394e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0003888032871083774</v>
+        <v>0.0002084823254956819</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0003578277678001035</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.001049867869509805</v>
+        <v>0.001788676400959999</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.0007387033227951201</v>
+        <v>0.0006767079074771365</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.84929356358044e-05</v>
+        <v>0.000392670157068059</v>
       </c>
       <c r="AB8" t="n">
         <v>4.032258064516625e-05</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.0008609625668449139</v>
+        <v>0.000852169808213754</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.002989157954308516</v>
+        <v>0.00713318670576738</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.01782339631780307</v>
+        <v>0.02334030236491809</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.001364511064971946</v>
+        <v>4.545454545454575e-05</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.0009196869274316261</v>
+        <v>0.0009126831291569632</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.001337234698312206</v>
+        <v>0.0001610746938071533</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.002769344710588997</v>
+        <v>0.001153067392893403</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.02877602133185263</v>
+        <v>0.02431792996919049</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.0003711479198767437</v>
+        <v>0.0003609625668448913</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.00926803092050878</v>
+        <v>0.005197087571444522</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>0.0005483825531714615</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.002756933667870429</v>
+        <v>0.0005872057207551794</v>
       </c>
       <c r="AP8" t="n">
+        <v>7.367387033399564e-05</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0.0004229731873710896</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0.01314898902002971</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0.0003227541689079683</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0.0001916801147570146</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0.0003025415444770418</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0.000457039858404637</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>8.064516129035749e-05</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0.0006989753422756012</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0.0002671321352639727</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0.0008968714651425985</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0.0002085561497326166</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0.0001210837185413344</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0.003555536356660449</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0.0002644589943758879</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0.0003208556149732367</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0.003299284748864584</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>-3.50733594650654e-06</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0.0001662049861495763</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0.0004880229358353916</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>0.0008485962355029381</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>-8.068854222700872e-05</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>0.0004632916259946051</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>0.0005878852713043254</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>4.363001745200657e-05</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>0.000231519071217251</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>0.0001332467203245147</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>0.0001879681601791916</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>0.001151755040290811</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>0.001475393984455581</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>0.0005540001182131992</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>0.0004245575429626503</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>0.0001892013353877592</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>0.000175469530902686</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>0.0002836168732183703</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>3.683693516699782e-05</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>9.30362747864566e-05</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>0.000392670157068059</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>0.00027481397248664</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>8.326672684688675e-18</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>0.0004733586992950511</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>0.0003853247779876251</v>
+      </c>
+      <c r="CY8" t="n">
+        <v>0.0003764674239786825</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>0.000473851417399851</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>0.0002017213555674802</v>
+      </c>
+      <c r="DD8" t="n">
         <v>8.310249307478813e-05</v>
       </c>
-      <c r="AQ8" t="n">
-        <v>0.0002354788069074132</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>0.01458639647632934</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>0.0002181500872600661</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0.0004290471433328668</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>4.363001745201489e-05</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0.0005464025177299742</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0.001045852737414196</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>0.000767831312667147</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0.0002006158887236126</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>0.001130918968766292</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>0.0009545454545454606</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>0.0001363636363636373</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>0.0001209677419354988</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>5.296610169491789e-05</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>0.001353372434017616</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>0.0002914838432454603</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>0.0008236800134306777</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>0.003185834743017213</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>0.0007363424824157999</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>0.0004897609655291374</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>0.0007809936230033453</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>0.0003651577135794393</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>0.0001328909186052218</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>0.0001957352402517432</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>0.0009209303906462491</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>0.0002143851748707376</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>9.406431925577386e-05</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>0.0002371507775298654</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>0.0003012477718359801</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>0.0005983066497644463</v>
-      </c>
-      <c r="BZ8" t="n">
-        <v>0.002065105815885368</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>0.0005753694439652596</v>
-      </c>
-      <c r="CB8" t="n">
-        <v>4.163336342344337e-17</v>
-      </c>
-      <c r="CC8" t="n">
-        <v>0.0005794126728040333</v>
-      </c>
-      <c r="CD8" t="n">
-        <v>0.0007670522576697341</v>
-      </c>
-      <c r="CE8" t="n">
-        <v>8.455467869222799e-05</v>
-      </c>
-      <c r="CF8" t="n">
-        <v>0.0001554480091340377</v>
-      </c>
-      <c r="CG8" t="n">
-        <v>0.0001281661727326078</v>
-      </c>
-      <c r="CH8" t="n">
-        <v>0.0005294117647058783</v>
-      </c>
-      <c r="CI8" t="n">
-        <v>9.234335114828573e-05</v>
-      </c>
-      <c r="CJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK8" t="n">
-        <v>0.0004117647058823448</v>
-      </c>
-      <c r="CL8" t="n">
-        <v>0.0002755139134005685</v>
-      </c>
-      <c r="CM8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN8" t="n">
-        <v>0.0001554480091340377</v>
-      </c>
-      <c r="CO8" t="n">
-        <v>4.032258064518291e-05</v>
-      </c>
-      <c r="CP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ8" t="n">
-        <v>0.0007540902574539266</v>
-      </c>
-      <c r="CR8" t="n">
-        <v>0.000621873586461999</v>
-      </c>
-      <c r="CS8" t="n">
-        <v>0.0001377358955514829</v>
-      </c>
-      <c r="CT8" t="n">
-        <v>0.0001177394034537066</v>
-      </c>
-      <c r="CU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CY8" t="n">
-        <v>0.000186594208485863</v>
-      </c>
-      <c r="CZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DD8" t="n">
-        <v>5.46334024766948e-05</v>
-      </c>
       <c r="DE8" t="n">
-        <v>3.68369351669895e-05</v>
+        <v>4.155124653739407e-05</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.0003624091235733206</v>
+        <v>0.0003030998407090258</v>
       </c>
       <c r="DG8" t="n">
-        <v>5.296610169491789e-05</v>
+        <v>0.0002773763611442492</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.001734588940471338</v>
+        <v>0.001104181788555245</v>
       </c>
       <c r="DI8" t="n">
-        <v>4.545454545454575e-05</v>
+        <v>0.0001604278074866184</v>
       </c>
       <c r="DJ8" t="n">
-        <v>4.010695187165459e-05</v>
+        <v>0</v>
       </c>
       <c r="DK8" t="n">
-        <v>0.0002109048601195235</v>
+        <v>-1.336898395722097e-05</v>
       </c>
       <c r="DL8" t="n">
         <v>0</v>
       </c>
       <c r="DM8" t="n">
-        <v>4.363001745201489e-05</v>
+        <v>0</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.002631425777612282</v>
+        <v>0.000335885833623345</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.0005604776579352932</v>
+        <v>0.001650833131966864</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.001794396080110413</v>
+        <v>0.0008529411764705869</v>
       </c>
       <c r="DQ8" t="n">
         <v>0</v>
@@ -4387,10 +4387,10 @@
         <v>0</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.001629848189009292</v>
+        <v>0.0007467806918356357</v>
       </c>
       <c r="DU8" t="n">
-        <v>0.0009383952407560515</v>
+        <v>0.0007871414299985751</v>
       </c>
       <c r="DV8" t="n">
         <v>0</v>
@@ -4399,25 +4399,25 @@
         <v>0</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.0001569858712716088</v>
+        <v>4.032258064516625e-05</v>
       </c>
       <c r="DY8" t="n">
-        <v>0.001409762444388479</v>
+        <v>0.001958319762982899</v>
       </c>
       <c r="DZ8" t="n">
         <v>0</v>
       </c>
       <c r="EA8" t="n">
-        <v>0</v>
+        <v>9.09090909090915e-05</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.0005814684193157754</v>
+        <v>0.0003969852137391344</v>
       </c>
       <c r="EC8" t="n">
-        <v>4.363001745201489e-05</v>
+        <v>4.155124653737741e-05</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.0003023237266934986</v>
+        <v>0</v>
       </c>
       <c r="EE8" t="n">
         <v>0</v>
@@ -4426,7 +4426,7 @@
         <v>0</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.0001612903225806734</v>
+        <v>7.849293563579607e-05</v>
       </c>
       <c r="EH8" t="n">
         <v>0</v>
@@ -4435,7 +4435,7 @@
         <v>0</v>
       </c>
       <c r="EJ8" t="n">
-        <v>8.310249307478813e-05</v>
+        <v>4.155124653739407e-05</v>
       </c>
       <c r="EK8" t="n">
         <v>0</v>
@@ -4444,7 +4444,7 @@
         <v>0</v>
       </c>
       <c r="EM8" t="n">
-        <v>0</v>
+        <v>4.034427111349604e-05</v>
       </c>
       <c r="EN8" t="n">
         <v>0</v>
@@ -4456,7 +4456,7 @@
         <v>0</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.000414450919312595</v>
+        <v>0.0002017213555674802</v>
       </c>
       <c r="ER8" t="n">
         <v>0</v>
@@ -4465,10 +4465,10 @@
         <v>0</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.0002811819516888997</v>
+        <v>0</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.0001662049861495763</v>
+        <v>0</v>
       </c>
       <c r="EV8" t="n">
         <v>0</v>
@@ -4477,7 +4477,7 @@
         <v>0</v>
       </c>
       <c r="EX8" t="n">
-        <v>0.0001059322033898358</v>
+        <v>0</v>
       </c>
       <c r="EY8" t="n">
         <v>0</v>
@@ -4490,466 +4490,466 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.003636363636363616</v>
+        <v>0.004447933019361605</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0006802721088435715</v>
+        <v>0.0001075847229693228</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002849462365591449</v>
+        <v>0.001866404715127701</v>
       </c>
       <c r="E9" t="n">
-        <v>0.004086021505376391</v>
+        <v>0.002210216110019658</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>0.0001569858712715866</v>
       </c>
       <c r="G9" t="n">
-        <v>0.004354838709677455</v>
+        <v>0.006612903225806477</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0005913978494624273</v>
+        <v>0.0001163467132053508</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001517530088958707</v>
+        <v>0.002773417059131367</v>
       </c>
       <c r="J9" t="n">
-        <v>0.004819944598337933</v>
+        <v>0.001495844875346242</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0008144269924375668</v>
+        <v>0.0006802721088435271</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0008144269924375668</v>
+        <v>0.0004653868528214034</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0003490401396161191</v>
+        <v>0.0002093144950287673</v>
       </c>
       <c r="N9" t="n">
-        <v>0.001828254847645427</v>
+        <v>0.004193548387096823</v>
       </c>
       <c r="O9" t="n">
-        <v>0.00275423728813563</v>
+        <v>0.0001108033240997064</v>
       </c>
       <c r="P9" t="n">
-        <v>0.001341807909604564</v>
+        <v>0.004029304029304038</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.007165775401069519</v>
+        <v>0.007634408602150589</v>
       </c>
       <c r="R9" t="n">
+        <v>0.0002326934264107017</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.002459445316588183</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.001337987201861568</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.001337987201861579</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.00510752688172047</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.0001745200698080263</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.00481423338566197</v>
+      </c>
+      <c r="Y9" t="n">
         <v>0.0003878116343490112</v>
       </c>
-      <c r="S9" t="n">
-        <v>0.0008310249307479034</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0.001570680628272347</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0.0009307737056428955</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0.001666666666666739</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0.0008474576271186752</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0.003490401396160636</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
       <c r="Z9" t="n">
-        <v>0.002780748663101584</v>
+        <v>0.002936288088642636</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.002268760907504453</v>
+        <v>0.002204301075268855</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0002824858757062287</v>
+        <v>0.0006876227897839038</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.006989247311827995</v>
+        <v>0.007741935483870999</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.01198325484039774</v>
+        <v>0.01102493074792242</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.02545454545454542</v>
+        <v>0.04299168975069249</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.006638418079096065</v>
+        <v>0.009745762711864347</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.001624293785310749</v>
+        <v>0.00167451596023025</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.003048128342245948</v>
+        <v>0.00167451596023025</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.000776836158192118</v>
+        <v>0.0004237288135592765</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.01631355932203392</v>
+        <v>0.01343804537521817</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.06088642659279778</v>
+        <v>0.0650415512465374</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.003172043010752745</v>
+        <v>0.001451612903225841</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.02467741935483875</v>
+        <v>0.01903225806451615</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.002258064516129077</v>
+        <v>0.006505376344086067</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.004709576138147609</v>
+        <v>0.002484848484848501</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.00053475935828875</v>
+        <v>0.0003878116343490112</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.0009139784946236906</v>
+        <v>0.00308738880167454</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.04803324099722991</v>
+        <v>0.03418282548476452</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.00105263157894735</v>
+        <v>0.0009677419354839234</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.002352941176470569</v>
+        <v>0.003244374672946126</v>
       </c>
       <c r="AU9" t="n">
+        <v>0.0004911591355599487</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0.003663003663003683</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0.003924646781789676</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0.001308215593929896</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0.001570680628272292</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0.002903225806451659</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0.006149584487534598</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0.01521505376344088</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0.0003225806451613189</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0.0001108033240997175</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0.0009019165727169876</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0.01204301075268821</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0.00141287284144429</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0.002105263157894721</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>0.02263440860215058</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0.0002908667830133771</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0.002668759811616983</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0.003610675039246491</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>0.00221606648199445</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>0.0001745200698080263</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0.0007858546168958869</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0.001080550098231836</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>0.0003878116343490112</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>0.0009972299168974686</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>0.002111984282907664</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0.0003324099722991525</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>0.000121212121212122</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>0.0008840864440078589</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>0.003602150537634452</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>0.005322580645161334</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>0.003157894736842093</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>0.0005402750491159458</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>0.001108033240997197</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>0.00434327577184721</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>0.003192046049188913</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>0.0007858546168958869</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>0.001831501831501836</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>0.001274238227146796</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>0.001059322033898258</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>0.0004709576138147376</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>0.0003765465303926296</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>0.00481423338566197</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>0.001569858712715855</v>
+      </c>
+      <c r="CN9" t="n">
         <v>0.0004986149584487287</v>
       </c>
-      <c r="AV9" t="n">
-        <v>0.006684491978609608</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0.004462365591397876</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>9.823182711197199e-05</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>0.004973262032085546</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0.001612903225806495</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>0.003933518005540149</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>0.00612903225806456</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>0.0009419152276295639</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>0.001122994652406417</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>0.0004509582863585493</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>0.01156462585034018</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>0.001883830455259083</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>0.001628853984875023</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>0.01403225806451618</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>0.002311827956989288</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>0.003315508021390334</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>0.000756253635834847</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>0.003172043010752723</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>0.001818181818181808</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>0.005161290322580692</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>0.000481283422459855</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>0.00326869806094181</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>0.001977894124491075</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>0.0007326007326007855</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>0.000666666666666671</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>0.0002118644067797049</v>
-      </c>
-      <c r="BW9" t="n">
+      <c r="CO9" t="n">
+        <v>0.002250130821559404</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>5.376344086022167e-05</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>0.001308215593929896</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>0.0005893909626719207</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>0.002437673130193896</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>0.0004653868528214034</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>5.540166204985875e-05</v>
+      </c>
+      <c r="CV9" t="n">
         <v>0.0001075268817204433</v>
       </c>
-      <c r="BX9" t="n">
-        <v>0.002048022598870081</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>0.003035060177917359</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>0.01000000000000003</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>0.003545706371191115</v>
-      </c>
-      <c r="CB9" t="n">
-        <v>0.0004653868528214699</v>
-      </c>
-      <c r="CC9" t="n">
-        <v>0.001412429378531122</v>
-      </c>
-      <c r="CD9" t="n">
-        <v>0.002385107620709803</v>
-      </c>
-      <c r="CE9" t="n">
-        <v>0.0005540166204985875</v>
-      </c>
-      <c r="CF9" t="n">
-        <v>0.001016042780748661</v>
-      </c>
-      <c r="CG9" t="n">
-        <v>0.000242424242424244</v>
-      </c>
-      <c r="CH9" t="n">
-        <v>0.001935483870967802</v>
-      </c>
-      <c r="CI9" t="n">
-        <v>0.002036067481093751</v>
-      </c>
-      <c r="CJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK9" t="n">
-        <v>0.002094240837696426</v>
-      </c>
-      <c r="CL9" t="n">
-        <v>0.001454333915066996</v>
-      </c>
-      <c r="CM9" t="n">
-        <v>0.0007526881720430589</v>
-      </c>
-      <c r="CN9" t="n">
-        <v>0.0004301075268817622</v>
-      </c>
-      <c r="CO9" t="n">
-        <v>0.0003139717425432065</v>
-      </c>
-      <c r="CP9" t="n">
-        <v>0.0001046572475144059</v>
-      </c>
-      <c r="CQ9" t="n">
-        <v>0.002365591397849498</v>
-      </c>
-      <c r="CR9" t="n">
-        <v>0.002192513368983939</v>
-      </c>
-      <c r="CS9" t="n">
-        <v>0.001344086021505431</v>
-      </c>
-      <c r="CT9" t="n">
-        <v>0.0008064516129032695</v>
-      </c>
-      <c r="CU9" t="n">
-        <v>0.0001069518716577456</v>
-      </c>
-      <c r="CV9" t="n">
-        <v>0.000424242424242427</v>
-      </c>
       <c r="CW9" t="n">
         <v>0</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.003036723163841837</v>
+        <v>0.001717451523545699</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.0006399069226295184</v>
+        <v>0.002271468144044309</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.0003763440860215184</v>
+        <v>0.0001163467132053508</v>
       </c>
       <c r="DA9" t="n">
         <v>0</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.0005756148613291989</v>
+        <v>0.002459445316588183</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.0003208556149732478</v>
+        <v>0.002982731554160145</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.00024557956777993</v>
+        <v>0.0006980802792321162</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.001454333915066996</v>
+        <v>0.0002688172043011083</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.0006279434850863907</v>
+        <v>0.0009942438513867225</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.001129032258064566</v>
+        <v>0.001308215593929885</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.005318559556786706</v>
+        <v>0.002799607072691568</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.001046572475143948</v>
+        <v>0.004657247514390372</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.0008144269924375447</v>
+        <v>0.0005379236148466138</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.002043010752688223</v>
+        <v>0</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.0002150537634408867</v>
+        <v>0.0003324099722991525</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.0006989247311828484</v>
+        <v>0.0009418282548476098</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.003490304709141267</v>
+        <v>0.001385041551246524</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.003656509695290833</v>
+        <v>0.004819944598337922</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.005927977839335174</v>
+        <v>0.002048022598870025</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.0004237288135593431</v>
+        <v>9.823182711199419e-05</v>
       </c>
       <c r="DR9" t="n">
         <v>0</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.00060606060606061</v>
+        <v>0.0005347593582887278</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.003796791443850256</v>
+        <v>0.002701375245579574</v>
       </c>
       <c r="DU9" t="n">
-        <v>0.009030470914127408</v>
+        <v>0.002603143418467602</v>
       </c>
       <c r="DV9" t="n">
         <v>0</v>
       </c>
       <c r="DW9" t="n">
-        <v>0</v>
+        <v>0.0003139717425431621</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.001666666666666716</v>
+        <v>0.001203558346415501</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.005494505494505553</v>
+        <v>0.009861495844875324</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0</v>
+        <v>0.0001569858712715755</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.000181818181818183</v>
+        <v>0.0002689618074233069</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.003475935828876986</v>
+        <v>0.008144044321329636</v>
       </c>
       <c r="EC9" t="n">
-        <v>0.0005649717514124575</v>
+        <v>0.0006802721088435493</v>
       </c>
       <c r="ED9" t="n">
-        <v>0.0006648199445983049</v>
+        <v>0.0004432132963988811</v>
       </c>
       <c r="EE9" t="n">
         <v>0</v>
       </c>
       <c r="EF9" t="n">
-        <v>5.376344086022167e-05</v>
+        <v>2.220446049250313e-17</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.001176470588235279</v>
+        <v>0.0002151694459386455</v>
       </c>
       <c r="EH9" t="n">
-        <v>0.0004709576138147931</v>
+        <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.0002093144950288117</v>
+        <v>0</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.001612903225806506</v>
+        <v>0.0005913978494624161</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.0001569858712716088</v>
+        <v>0.001203558346415479</v>
       </c>
       <c r="EL9" t="n">
         <v>0</v>
       </c>
       <c r="EM9" t="n">
-        <v>0.0004653868528214699</v>
+        <v>0.0003763440860215294</v>
       </c>
       <c r="EN9" t="n">
-        <v>0.000116346713205373</v>
+        <v>0</v>
       </c>
       <c r="EO9" t="n">
         <v>0</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.000483870967741995</v>
+        <v>0</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.002245989304812801</v>
+        <v>0.001151229722658287</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.000121212121212122</v>
+        <v>0</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.000116346713205373</v>
+        <v>6.0606060606061e-05</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.001283422459893036</v>
+        <v>0.002150537634408645</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.001451612903225852</v>
+        <v>0.00252688172043013</v>
       </c>
       <c r="EV9" t="n">
         <v>0</v>
       </c>
       <c r="EW9" t="n">
-        <v>0.0004237288135593431</v>
+        <v>0.0002616431187859703</v>
       </c>
       <c r="EX9" t="n">
-        <v>0.0006417112299465066</v>
+        <v>0</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.000242424242424244</v>
+        <v>0.0002688172043011083</v>
       </c>
     </row>
   </sheetData>
